--- a/data/administracion_de_tribunales/OP_LEY148Archivadas.xlsx
+++ b/data/administracion_de_tribunales/OP_LEY148Archivadas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\administracion_de_tribunales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE5630A-5D55-4BF9-BAEF-7F2CACC54D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6496A069-EFF6-47C9-AE65-D3BA06C6D5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-2021" sheetId="5" r:id="rId1"/>
@@ -463,7 +463,10 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1">
+        <f>SUM(C2:D2)</f>
+        <v>0</v>
+      </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -471,6 +474,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
+        <f t="shared" ref="B3:B15" si="0">SUM(C3:D3)</f>
         <v>1</v>
       </c>
       <c r="D3" s="1">
@@ -482,6 +486,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D4" s="1">
@@ -493,6 +498,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C5" s="1">
@@ -507,6 +513,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="1">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C6" s="1">
@@ -518,6 +525,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C7" s="1">
@@ -531,7 +539,10 @@
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
@@ -539,7 +550,10 @@
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
@@ -547,28 +561,40 @@
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1"/>
+      <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="1"/>
+      <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -576,6 +602,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="1">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C14">
@@ -589,7 +616,10 @@
       <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="1"/>
+      <c r="B15" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -642,12 +672,17 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B2">
+        <f>SUM(C2:D2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
+        <f t="shared" ref="B3:B15" si="0">SUM(C3:D3)</f>
         <v>1</v>
       </c>
       <c r="D3">
@@ -659,6 +694,7 @@
         <v>6</v>
       </c>
       <c r="B4">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C4">
@@ -670,6 +706,7 @@
         <v>18</v>
       </c>
       <c r="B5">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C5">
@@ -683,17 +720,26 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D8">
@@ -704,27 +750,44 @@
       <c r="A9" t="s">
         <v>11</v>
       </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13">
@@ -735,12 +798,17 @@
       <c r="A14" t="s">
         <v>16</v>
       </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D15">
@@ -810,6 +878,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="3">
+        <f>SUM(C2:D2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="3">
@@ -822,6 +891,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="3">
+        <f t="shared" ref="B3:B14" si="0">SUM(C3:D3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="3">
@@ -833,7 +903,10 @@
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
@@ -842,6 +915,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C5" s="3"/>
@@ -853,7 +927,10 @@
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
@@ -861,7 +938,10 @@
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
@@ -869,7 +949,10 @@
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
@@ -878,6 +961,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C9" s="3"/>
@@ -889,7 +973,10 @@
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
@@ -898,6 +985,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C11" s="3">
@@ -911,7 +999,10 @@
       <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
@@ -920,6 +1011,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C13" s="3"/>
@@ -932,6 +1024,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C14" s="3"/>
@@ -998,17 +1091,26 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B2">
+        <f>SUM(C2:D2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B15" si="0">SUM(C3:D3)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D4">
@@ -1020,6 +1122,7 @@
         <v>7</v>
       </c>
       <c r="B5">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C5">
@@ -1034,6 +1137,7 @@
         <v>8</v>
       </c>
       <c r="B6">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D6">
@@ -1044,12 +1148,17 @@
       <c r="A7" t="s">
         <v>9</v>
       </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D8">
@@ -1061,6 +1170,7 @@
         <v>11</v>
       </c>
       <c r="B9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9">
@@ -1071,17 +1181,26 @@
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C12">
@@ -1092,12 +1211,17 @@
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D14">
@@ -1108,6 +1232,10 @@
       <c r="A15" t="s">
         <v>17</v>
       </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1118,11 +1246,11 @@
         <v>13</v>
       </c>
       <c r="C16">
-        <f t="shared" ref="C16:D16" si="0">SUM(C4:C14)</f>
+        <f t="shared" ref="C16:D16" si="1">SUM(C4:C14)</f>
         <v>3</v>
       </c>
       <c r="D16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -1167,32 +1295,60 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B2">
+        <f>SUM(C2:D2)</f>
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
+        <f t="shared" ref="B3:B15" si="0">SUM(C3:D3)</f>
+        <v>4</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1200,29 +1356,44 @@
         <v>8</v>
       </c>
       <c r="B6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>4</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>1</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1230,27 +1401,55 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
@@ -1262,21 +1461,39 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1284,15 +1501,15 @@
       </c>
       <c r="B16">
         <f>SUM(B2:B15)</f>
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="C16">
-        <f t="shared" ref="C16:D16" si="0">SUM(C2:C15)</f>
-        <v>6</v>
+        <f t="shared" ref="C16:D16" si="1">SUM(C2:C15)</f>
+        <v>24</v>
       </c>
       <c r="D16">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
